--- a/astro-site/public/dl/restaurant-schedule-templates/04-new-hire-onboarding-checklist.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/04-new-hire-onboarding-checklist.xlsx
@@ -212,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,6 +312,9 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -987,7 +990,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>2</v>
       </c>
@@ -1014,7 +1017,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="10" t="n">
         <v>3</v>
       </c>
@@ -1041,7 +1044,7 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>4</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="n">
         <v>5</v>
       </c>
@@ -1149,7 +1152,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>8</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>9</v>
       </c>
@@ -1230,11 +1233,11 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" t="n">
         <v>11</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="53" t="inlineStr">
         <is>
           <t>State new-hire report filed (federal limit: 20 days after hire; some states sooner)</t>
         </is>
@@ -1257,11 +1260,11 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" t="n">
         <v>12</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="53" t="inlineStr">
         <is>
           <t>Workers' comp: injury-reporting procedure and required workplace posters shown</t>
         </is>
@@ -1284,11 +1287,11 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" t="n">
         <v>13</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="53" t="inlineStr">
         <is>
           <t>Form W-4 and state withholding form signed (needed for the first payroll)</t>
         </is>
@@ -1311,6 +1314,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="37" t="inlineStr">
         <is>
@@ -1361,7 +1365,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>1</v>
       </c>
@@ -1415,7 +1419,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="10" t="n">
         <v>3</v>
       </c>
@@ -1442,7 +1446,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="10" t="n">
         <v>4</v>
       </c>
@@ -1469,7 +1473,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="10" t="n">
         <v>5</v>
       </c>
@@ -1496,7 +1500,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="10" t="n">
         <v>6</v>
       </c>
@@ -1550,7 +1554,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="10" t="n">
         <v>8</v>
       </c>
@@ -1577,6 +1581,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="39" t="inlineStr">
         <is>
@@ -1843,7 +1848,7 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="10" t="n">
         <v>9</v>
       </c>
@@ -1870,6 +1875,7 @@
         <v/>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="42" t="inlineStr">
         <is>
@@ -2244,6 +2250,7 @@
         <v/>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="44" t="inlineStr">
         <is>
@@ -2592,7 +2599,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F7:F19 F23:F30 F34:F42 F46:F57 F61:F68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid mark" error="✓ done · ✗ pending · — not applicable to this position." promptTitle="kitgp-v2b · Done" prompt="Mark &quot;—&quot; on anything that does NOT apply to this position (a line cook does not need POS access): those tasks leave the denominator and progress can reach 100%." type="list" errorStyle="stop">
+    <dataValidation sqref="F7:F19 F23:F30 F34:F42 F46:F57 F61:F68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid mark" error="✓ done · ✗ pending · — not applicable to this position." promptTitle="Task done" prompt="Mark &quot;—&quot; on anything that does NOT apply to this position (a line cook does not need POS access): those tasks leave the denominator and progress can reach 100%." type="list" errorStyle="stop">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
